--- a/Dummy-Excel.xlsx
+++ b/Dummy-Excel.xlsx
@@ -1,26 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="16729"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Family\Desktop\xls\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\excel-test\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B997302-D3E7-47A5-A054-C0D7E6B3F38C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="1116" yWindow="1116" windowWidth="17280" windowHeight="8880" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sample Data" sheetId="1" r:id="rId1"/>
     <sheet name="Dummy Formulas" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t>ID</t>
   </si>
@@ -37,21 +51,6 @@
     <t>Salary</t>
   </si>
   <si>
-    <t>John</t>
-  </si>
-  <si>
-    <t>Sarah</t>
-  </si>
-  <si>
-    <t>Mike</t>
-  </si>
-  <si>
-    <t>Emma</t>
-  </si>
-  <si>
-    <t>David</t>
-  </si>
-  <si>
     <t>HR</t>
   </si>
   <si>
@@ -83,14 +82,32 @@
   </si>
   <si>
     <t>Value 3</t>
+  </si>
+  <si>
+    <t>Lazar Test</t>
+  </si>
+  <si>
+    <t>Mike Test</t>
+  </si>
+  <si>
+    <t>Selena Test</t>
+  </si>
+  <si>
+    <t>Emma Test</t>
+  </si>
+  <si>
+    <t>David Test</t>
+  </si>
+  <si>
+    <t>D</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="6" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -117,7 +134,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -140,16 +157,30 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="6" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -168,9 +199,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -208,9 +239,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -243,26 +274,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -295,26 +309,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -487,11 +484,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -508,86 +505,86 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="C2">
         <v>30</v>
       </c>
       <c r="D2" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E2" s="2">
         <v>50000</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="C3">
         <v>28</v>
       </c>
       <c r="D3" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E3" s="2">
         <v>55000</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="C4">
         <v>35</v>
       </c>
       <c r="D4" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E4" s="2">
         <v>60000</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C5">
         <v>25</v>
       </c>
       <c r="D5" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E5" s="2">
         <v>52000</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="C6">
         <v>40</v>
       </c>
       <c r="D6" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E6" s="2">
         <v>70000</v>
@@ -599,24 +596,27 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:D4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="B2">
         <v>10</v>
@@ -625,10 +625,13 @@
         <f>B2+B3</f>
         <v>30</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="B3">
         <v>20</v>
@@ -637,10 +640,13 @@
         <f>B3*2</f>
         <v>40</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D3">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B4">
         <v>30</v>
@@ -648,6 +654,9 @@
       <c r="C4">
         <f>B4+10</f>
         <v>40</v>
+      </c>
+      <c r="D4">
+        <v>60</v>
       </c>
     </row>
   </sheetData>

--- a/Dummy-Excel.xlsx
+++ b/Dummy-Excel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\excel-test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B997302-D3E7-47A5-A054-C0D7E6B3F38C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47C8B48C-5D6C-4228-957E-E198A3E0CC3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1116" yWindow="1116" windowWidth="17280" windowHeight="8880" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1116" yWindow="1116" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sample Data" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
   <si>
     <t>ID</t>
   </si>
@@ -100,6 +100,12 @@
   </si>
   <si>
     <t>D</t>
+  </si>
+  <si>
+    <t>Ela</t>
+  </si>
+  <si>
+    <t>Cats</t>
   </si>
 </sst>
 </file>
@@ -178,7 +184,7 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -485,7 +491,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
@@ -588,6 +594,23 @@
       </c>
       <c r="E6" s="2">
         <v>70000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7">
+        <v>22</v>
+      </c>
+      <c r="D7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E7" s="2">
+        <v>99999</v>
       </c>
     </row>
   </sheetData>
